--- a/E/SWADPR.xlsx
+++ b/E/SWADPR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
@@ -29,6 +29,15 @@
   </si>
   <si>
     <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20143587</t>
+  </si>
+  <si>
+    <t>MJI HP HAIKYU P/CARD</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -421,11 +430,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -471,6 +480,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
